--- a/elo/knapsack/excel365/fuzzy_match.xlsx
+++ b/elo/knapsack/excel365/fuzzy_match.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="370" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="361" uniqueCount="130">
   <si>
     <t>name</t>
   </si>
@@ -28,106 +28,160 @@
     <t>country</t>
   </si>
   <si>
-    <t>BOLGER Kevin</t>
-  </si>
-  <si>
-    <t>DIEKMANN Logan</t>
-  </si>
-  <si>
-    <t>PATTERSON Scott</t>
-  </si>
-  <si>
-    <t>WONDERS Hunter</t>
-  </si>
-  <si>
-    <t>O CONNELL Finn</t>
-  </si>
-  <si>
-    <t>JORTBERG Lauren</t>
-  </si>
-  <si>
-    <t>BERANOVA Tereza</t>
-  </si>
-  <si>
-    <t>JANATOVA Katerina</t>
-  </si>
-  <si>
-    <t>RAZYMOVA Katerina</t>
-  </si>
-  <si>
-    <t>SELLER Ludek</t>
-  </si>
-  <si>
-    <t>MRKONJIC Lukas</t>
-  </si>
-  <si>
-    <t>VERMEULEN Mika</t>
-  </si>
-  <si>
-    <t>LEODOLTER Philipp</t>
-  </si>
-  <si>
-    <t>FOETTINGER Michael</t>
-  </si>
-  <si>
-    <t>UNTERWEGER Lisa</t>
-  </si>
-  <si>
-    <t>BOEGL Lucas</t>
-  </si>
-  <si>
-    <t>BRUGGER Janosch</t>
-  </si>
-  <si>
-    <t>MOCH Friedrich</t>
-  </si>
-  <si>
-    <t>DOBLER Jonas</t>
-  </si>
-  <si>
-    <t>NOTZ Florian</t>
-  </si>
-  <si>
-    <t>KUCHLER Albert</t>
-  </si>
-  <si>
-    <t>CARL Victoria</t>
-  </si>
-  <si>
-    <t>HENNIG Katharina</t>
-  </si>
-  <si>
-    <t>FINK Pia</t>
-  </si>
-  <si>
-    <t>GIMMLER Laura</t>
-  </si>
-  <si>
-    <t>KREHL Sofie</t>
-  </si>
-  <si>
-    <t>RYDZEK Coletta</t>
-  </si>
-  <si>
-    <t>SAUERBREY Katherine</t>
-  </si>
-  <si>
-    <t>UREVC Eva</t>
-  </si>
-  <si>
-    <t>MANDELJC Anja</t>
-  </si>
-  <si>
-    <t>KLEMENCIC Anita</t>
-  </si>
-  <si>
-    <t>ZERJAV Neza</t>
-  </si>
-  <si>
-    <t>SIMENC Miha</t>
-  </si>
-  <si>
-    <t>LICEF Miha</t>
+    <t>ANDERSSON Ebba</t>
+  </si>
+  <si>
+    <t>DAHLQVIST Maja</t>
+  </si>
+  <si>
+    <t>HAGSTROEM Johanna</t>
+  </si>
+  <si>
+    <t>HENRIKSSON Sofia</t>
+  </si>
+  <si>
+    <t>ILAR Moa</t>
+  </si>
+  <si>
+    <t>KARLSSON Frida</t>
+  </si>
+  <si>
+    <t>LUNDGREN Moa</t>
+  </si>
+  <si>
+    <t>RIBOM Emma</t>
+  </si>
+  <si>
+    <t>ROSENBERG Maerta</t>
+  </si>
+  <si>
+    <t>SVAHN Linn</t>
+  </si>
+  <si>
+    <t>ANGER Edvin</t>
+  </si>
+  <si>
+    <t>BERGLUND Gustaf</t>
+  </si>
+  <si>
+    <t>BURMAN Jens</t>
+  </si>
+  <si>
+    <t>DANIELSSON Emil</t>
+  </si>
+  <si>
+    <t>ERSSON George</t>
+  </si>
+  <si>
+    <t>HALFVARSSON Calle</t>
+  </si>
+  <si>
+    <t>HAEGGSTROEM Johan</t>
+  </si>
+  <si>
+    <t>JOHANSSON Leo</t>
+  </si>
+  <si>
+    <t>POROMAA William</t>
+  </si>
+  <si>
+    <t>SANDSTROEM Bjoern</t>
+  </si>
+  <si>
+    <t>SVENSSON Oskar</t>
+  </si>
+  <si>
+    <t>FRANCHI Francesca</t>
+  </si>
+  <si>
+    <t>GANZ Caterina</t>
+  </si>
+  <si>
+    <t>COMARELLA Anna</t>
+  </si>
+  <si>
+    <t>PELLEGRINO Federico</t>
+  </si>
+  <si>
+    <t>DE FABIANI Francesco</t>
+  </si>
+  <si>
+    <t>VENTURA Paolo</t>
+  </si>
+  <si>
+    <t>GRAZ Davide</t>
+  </si>
+  <si>
+    <t>DAPRA Simone</t>
+  </si>
+  <si>
+    <t>BARP Elia</t>
+  </si>
+  <si>
+    <t>HELLWEGER Michael</t>
+  </si>
+  <si>
+    <t>KARPPANEN Miro</t>
+  </si>
+  <si>
+    <t>LEPISTO Lauri</t>
+  </si>
+  <si>
+    <t>LIEKARI Emil</t>
+  </si>
+  <si>
+    <t>NISSINEN Vilma</t>
+  </si>
+  <si>
+    <t>RYYTTY Vilma</t>
+  </si>
+  <si>
+    <t>SAARI Amanda</t>
+  </si>
+  <si>
+    <t>AHONEN Olli</t>
+  </si>
+  <si>
+    <t>HAKOLA Ristomatti</t>
+  </si>
+  <si>
+    <t>HYVARINEN Perttu</t>
+  </si>
+  <si>
+    <t>LINDHOLM Remi</t>
+  </si>
+  <si>
+    <t>MOILANEN Niilo</t>
+  </si>
+  <si>
+    <t>MAKI Joni</t>
+  </si>
+  <si>
+    <t>NISKANEN Iivo</t>
+  </si>
+  <si>
+    <t>POIKONEN Verneri</t>
+  </si>
+  <si>
+    <t>RUUSKANEN Arsi</t>
+  </si>
+  <si>
+    <t>SUHONEN Verneri</t>
+  </si>
+  <si>
+    <t>VUORELA Markus</t>
+  </si>
+  <si>
+    <t>VUORINEN Lauri</t>
+  </si>
+  <si>
+    <t>AHONEN Ville</t>
+  </si>
+  <si>
+    <t>ANTTOLA Niko</t>
+  </si>
+  <si>
+    <t>HAARALA Juuso</t>
   </si>
   <si>
     <t>JOENSUU Jasmi</t>
@@ -136,157 +190,55 @@
     <t>KYLLONEN Anne</t>
   </si>
   <si>
-    <t>LAMSA Emmi</t>
+    <t>KAHARA Jasmin</t>
+  </si>
+  <si>
+    <t>LYLYNPERA Katri</t>
   </si>
   <si>
     <t>MATINTALO Johanna</t>
   </si>
   <si>
+    <t>NIEMELA Hilla</t>
+  </si>
+  <si>
     <t>NISKANEN Kerttu</t>
   </si>
   <si>
     <t>OLKKONEN Tiia</t>
   </si>
   <si>
-    <t>PAJUNOJA Maaret</t>
-  </si>
-  <si>
     <t>PIIPPO Eveliina</t>
   </si>
   <si>
     <t>PARMAKOSKI Krista</t>
   </si>
   <si>
-    <t>HAARALA Juuso</t>
-  </si>
-  <si>
-    <t>HAKOLA Ristomatti</t>
-  </si>
-  <si>
-    <t>HYVARINEN Perttu</t>
-  </si>
-  <si>
-    <t>LEPISTO Lauri</t>
-  </si>
-  <si>
-    <t>LINDHOLM Remi</t>
-  </si>
-  <si>
-    <t>MOILANEN Niilo</t>
-  </si>
-  <si>
-    <t>MAKI Joni</t>
-  </si>
-  <si>
-    <t>NISKANEN Iivo</t>
-  </si>
-  <si>
-    <t>POIKONEN Verneri</t>
-  </si>
-  <si>
-    <t>RUUSKANEN Arsi</t>
-  </si>
-  <si>
-    <t>SUHONEN Verneri</t>
-  </si>
-  <si>
-    <t>VUORELA Markus</t>
-  </si>
-  <si>
-    <t>VUORINEN Lauri</t>
-  </si>
-  <si>
-    <t>PELLEGRINO Federico</t>
-  </si>
-  <si>
-    <t>DE FABIANI Francesco</t>
-  </si>
-  <si>
-    <t>GRAZ Davide</t>
-  </si>
-  <si>
-    <t>MOCELLINI Simone</t>
-  </si>
-  <si>
-    <t>ABRAM Mikael</t>
-  </si>
-  <si>
-    <t>NOECKLER Dietmar</t>
-  </si>
-  <si>
-    <t>VENTURA Paolo</t>
-  </si>
-  <si>
-    <t>SALVADORI Giandomenico</t>
-  </si>
-  <si>
-    <t>DAPRA Simone</t>
-  </si>
-  <si>
-    <t>HELLWEGER Michael</t>
-  </si>
-  <si>
-    <t>CORADAZZI Martin</t>
-  </si>
-  <si>
-    <t>GANZ Caterina</t>
-  </si>
-  <si>
-    <t>PITTIN Cristina</t>
-  </si>
-  <si>
-    <t>FRANCHI Francesca</t>
-  </si>
-  <si>
-    <t>COMARELLA Anna</t>
-  </si>
-  <si>
-    <t>BELLINI Martina</t>
-  </si>
-  <si>
-    <t>SANFILIPPO Federica</t>
-  </si>
-  <si>
-    <t>ANGER Edvin</t>
-  </si>
-  <si>
-    <t>HALFVARSSON Calle</t>
-  </si>
-  <si>
-    <t>GRATE Marcus</t>
-  </si>
-  <si>
-    <t>HAEGGSTROEM Johan</t>
-  </si>
-  <si>
-    <t>ROSJOE Eric</t>
-  </si>
-  <si>
-    <t>ANDERSSON Ebba</t>
-  </si>
-  <si>
-    <t>DAHLQVIST Maja</t>
-  </si>
-  <si>
-    <t>HAGSTROEM Johanna</t>
-  </si>
-  <si>
-    <t>ILAR Moa</t>
-  </si>
-  <si>
-    <t>KARLSSON Frida</t>
-  </si>
-  <si>
-    <t>LUNDGREN Moa</t>
-  </si>
-  <si>
-    <t>RIBOM Emma</t>
-  </si>
-  <si>
-    <t>SUNDLING Jonna</t>
-  </si>
-  <si>
-    <t>SVAHN Linn</t>
+    <t>ALAKOSKI Anni</t>
+  </si>
+  <si>
+    <t>HAGER Julia</t>
+  </si>
+  <si>
+    <t>IMMONEN Rebecca</t>
+  </si>
+  <si>
+    <t>CLAUDEL Delphine</t>
+  </si>
+  <si>
+    <t>DOLCI Flora</t>
+  </si>
+  <si>
+    <t>DUCORDEAU Juliette</t>
+  </si>
+  <si>
+    <t>GAL Melissa</t>
+  </si>
+  <si>
+    <t>QUINTIN Lena</t>
+  </si>
+  <si>
+    <t>ARNAUD Julien</t>
   </si>
   <si>
     <t>CHANAVAT Lucas</t>
@@ -295,9 +247,6 @@
     <t>CHAPPAZ Jules</t>
   </si>
   <si>
-    <t>CHAUTEMPS Arnaud</t>
-  </si>
-  <si>
     <t>JAY Renaud</t>
   </si>
   <si>
@@ -310,118 +259,145 @@
     <t>LAPIERRE Jules</t>
   </si>
   <si>
-    <t>LOVERA Victor</t>
-  </si>
-  <si>
-    <t>PARISSE Clement</t>
-  </si>
-  <si>
-    <t>CLAUDEL Delphine</t>
-  </si>
-  <si>
-    <t>DOLCI Flora</t>
-  </si>
-  <si>
-    <t>DUCORDEAU Juliette</t>
-  </si>
-  <si>
-    <t>GAL Melissa</t>
-  </si>
-  <si>
-    <t>QUINTIN Lena</t>
+    <t>ROETHE Sjur</t>
+  </si>
+  <si>
+    <t>TOENSETH Didrik</t>
+  </si>
+  <si>
+    <t>ANDERSEN Iver Tildheim</t>
+  </si>
+  <si>
+    <t>DOENNESTAD Henrik</t>
+  </si>
+  <si>
+    <t>MOERK Martin Kirkeberg</t>
+  </si>
+  <si>
+    <t>SANDVIK Edvard</t>
+  </si>
+  <si>
+    <t>GUNNULFSEN Mikael</t>
+  </si>
+  <si>
+    <t>KORSAETH Amund</t>
+  </si>
+  <si>
+    <t>GOLBERG Paal</t>
+  </si>
+  <si>
+    <t>KLAEBO Johannes Hoesflot</t>
+  </si>
+  <si>
+    <t>NORTHUG Even</t>
+  </si>
+  <si>
+    <t>TAUGBOEL Haavard Solaas</t>
+  </si>
+  <si>
+    <t>VALNES Erik</t>
+  </si>
+  <si>
+    <t>ARNESEN Harald Astrup</t>
+  </si>
+  <si>
+    <t>HOLBAEK Mathias</t>
+  </si>
+  <si>
+    <t>HOLMBOE Aleksander Elde</t>
+  </si>
+  <si>
+    <t>SKAANES Haakon</t>
+  </si>
+  <si>
+    <t>JENSSEN Jan Thomas</t>
+  </si>
+  <si>
+    <t>KRUEGER Simen Hegstad</t>
+  </si>
+  <si>
+    <t>SLIND Astrid Oeyre</t>
+  </si>
+  <si>
+    <t>WENG Heidi</t>
+  </si>
+  <si>
+    <t>AMUNDSEN Hedda Oestberg</t>
+  </si>
+  <si>
+    <t>BERGANE Margrethe</t>
+  </si>
+  <si>
+    <t>HEGGEN Anna</t>
+  </si>
+  <si>
+    <t>WANGENSTEEN Maren</t>
+  </si>
+  <si>
+    <t>JOHNSEN Elena Rise</t>
   </si>
   <si>
     <t>AMUNDSEN Harald Oestberg</t>
   </si>
   <si>
-    <t>ANDERSEN Iver Tildheim</t>
-  </si>
-  <si>
-    <t>HOLUND Hans Christer</t>
-  </si>
-  <si>
-    <t>KRUEGER Simen Hegstad</t>
-  </si>
-  <si>
-    <t>ROETHE Sjur</t>
-  </si>
-  <si>
-    <t>TOENSETH Didrik</t>
-  </si>
-  <si>
-    <t>THEODORSEN Silje</t>
-  </si>
-  <si>
-    <t>WENG Heidi</t>
-  </si>
-  <si>
-    <t>OESTBERG Ingvild Flugstad</t>
+    <t>EVENSEN Ansgar</t>
   </si>
   <si>
     <t>JENSSEN Matz William</t>
   </si>
   <si>
-    <t>KLAEBO Johannes Hoesflot</t>
-  </si>
-  <si>
-    <t>NORTHUG Even</t>
-  </si>
-  <si>
-    <t>SKAR Sindre Bjoernestad</t>
-  </si>
-  <si>
-    <t>TAUGBOEL Haavard Solaas</t>
-  </si>
-  <si>
-    <t>VALNES Erik</t>
-  </si>
-  <si>
-    <t>JOHNSEN Elena Rise</t>
+    <t>FOSNAES Kristin Austgulen</t>
+  </si>
+  <si>
+    <t>WENG Lotta Udnes</t>
+  </si>
+  <si>
+    <t>ANDREASSEN Milla Grosberghaugen</t>
+  </si>
+  <si>
+    <t>DRIVENES Julie Bjervig</t>
+  </si>
+  <si>
+    <t>DYRHOVD Margrete Roessum</t>
+  </si>
+  <si>
+    <t>HAUGEN Helene Ekrheim</t>
   </si>
   <si>
     <t>MELLING Maria Hartz</t>
   </si>
   <si>
+    <t>SVENDSEN Anna</t>
+  </si>
+  <si>
+    <t>SKAANES Marte</t>
+  </si>
+  <si>
+    <t>KALVAA Anne Kjersti</t>
+  </si>
+  <si>
     <t>MYHRVOLD Mathilde</t>
   </si>
   <si>
-    <t>ROFSTAD Hanne Wilberg</t>
+    <t>SKISTAD Kristine Stavaas</t>
   </si>
   <si>
     <t>STENSETH Ane Appelkvist</t>
   </si>
   <si>
-    <t>KALVAA Anne Kjersti</t>
+    <t>f</t>
   </si>
   <si>
     <t>m</t>
   </si>
   <si>
-    <t>f</t>
-  </si>
-  <si>
-    <t>USA</t>
-  </si>
-  <si>
-    <t>CZE</t>
-  </si>
-  <si>
-    <t>AUT</t>
-  </si>
-  <si>
-    <t>DEU</t>
-  </si>
-  <si>
-    <t>SVN</t>
+    <t>SWE</t>
+  </si>
+  <si>
+    <t>ITA</t>
   </si>
   <si>
     <t>FIN</t>
-  </si>
-  <si>
-    <t>ITA</t>
-  </si>
-  <si>
-    <t>SWE</t>
   </si>
   <si>
     <t>FRA</t>
@@ -785,7 +761,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E123"/>
+  <dimension ref="A1:E120"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -810,13 +786,13 @@
         <v>4</v>
       </c>
       <c r="C2">
-        <v>3530713</v>
+        <v>3505990</v>
       </c>
       <c r="D2" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="E2" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -827,13 +803,13 @@
         <v>5</v>
       </c>
       <c r="C3">
-        <v>3530718</v>
+        <v>3505800</v>
       </c>
       <c r="D3" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="E3" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -844,13 +820,13 @@
         <v>6</v>
       </c>
       <c r="C4">
-        <v>3530532</v>
+        <v>3506105</v>
       </c>
       <c r="D4" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="E4" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -861,13 +837,13 @@
         <v>7</v>
       </c>
       <c r="C5">
-        <v>3530860</v>
+        <v>3505834</v>
       </c>
       <c r="D5" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="E5" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -878,13 +854,13 @@
         <v>8</v>
       </c>
       <c r="C6">
-        <v>3530872</v>
+        <v>3505998</v>
       </c>
       <c r="D6" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="E6" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -895,13 +871,13 @@
         <v>9</v>
       </c>
       <c r="C7">
-        <v>3535634</v>
+        <v>3506154</v>
       </c>
       <c r="D7" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="E7" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -912,13 +888,13 @@
         <v>10</v>
       </c>
       <c r="C8">
-        <v>3155344</v>
+        <v>3506079</v>
       </c>
       <c r="D8" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="E8" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -929,13 +905,13 @@
         <v>11</v>
       </c>
       <c r="C9">
-        <v>3155324</v>
+        <v>3506008</v>
       </c>
       <c r="D9" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="E9" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -946,13 +922,13 @@
         <v>12</v>
       </c>
       <c r="C10">
-        <v>3155314</v>
+        <v>3506356</v>
       </c>
       <c r="D10" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="E10" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -963,13 +939,13 @@
         <v>13</v>
       </c>
       <c r="C11">
-        <v>3150549</v>
+        <v>3506166</v>
       </c>
       <c r="D11" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="E11" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -980,13 +956,13 @@
         <v>14</v>
       </c>
       <c r="C12">
-        <v>3050281</v>
+        <v>3501976</v>
       </c>
       <c r="D12" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="E12" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -997,13 +973,13 @@
         <v>15</v>
       </c>
       <c r="C13">
-        <v>3050342</v>
+        <v>3501587</v>
       </c>
       <c r="D13" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="E13" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -1014,13 +990,13 @@
         <v>16</v>
       </c>
       <c r="C14">
-        <v>3050286</v>
+        <v>3501223</v>
       </c>
       <c r="D14" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="E14" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -1031,13 +1007,13 @@
         <v>17</v>
       </c>
       <c r="C15">
-        <v>3050256</v>
+        <v>3501871</v>
       </c>
       <c r="D15" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="E15" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -1048,13 +1024,13 @@
         <v>18</v>
       </c>
       <c r="C16">
-        <v>3055108</v>
+        <v>3501842</v>
       </c>
       <c r="D16" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="E16" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -1065,13 +1041,13 @@
         <v>19</v>
       </c>
       <c r="C17">
-        <v>3200205</v>
+        <v>3500664</v>
       </c>
       <c r="D17" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="E17" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -1082,13 +1058,13 @@
         <v>20</v>
       </c>
       <c r="C18">
-        <v>3200676</v>
+        <v>3501010</v>
       </c>
       <c r="D18" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="E18" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -1099,13 +1075,13 @@
         <v>21</v>
       </c>
       <c r="C19">
-        <v>3200802</v>
+        <v>3501662</v>
       </c>
       <c r="D19" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="E19" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -1116,13 +1092,13 @@
         <v>22</v>
       </c>
       <c r="C20">
-        <v>3200356</v>
+        <v>3501741</v>
       </c>
       <c r="D20" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="E20" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -1133,13 +1109,13 @@
         <v>23</v>
       </c>
       <c r="C21">
-        <v>3200376</v>
+        <v>3501297</v>
       </c>
       <c r="D21" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="E21" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -1150,13 +1126,13 @@
         <v>24</v>
       </c>
       <c r="C22">
-        <v>3200752</v>
+        <v>3501255</v>
       </c>
       <c r="D22" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="E22" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -1167,13 +1143,13 @@
         <v>25</v>
       </c>
       <c r="C23">
-        <v>3205403</v>
+        <v>3295370</v>
       </c>
       <c r="D23" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="E23" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -1184,13 +1160,13 @@
         <v>26</v>
       </c>
       <c r="C24">
-        <v>3205460</v>
+        <v>3295241</v>
       </c>
       <c r="D24" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="E24" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -1201,13 +1177,13 @@
         <v>27</v>
       </c>
       <c r="C25">
-        <v>3205407</v>
+        <v>3295322</v>
       </c>
       <c r="D25" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="E25" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -1218,13 +1194,13 @@
         <v>28</v>
       </c>
       <c r="C26">
-        <v>3205305</v>
+        <v>3290326</v>
       </c>
       <c r="D26" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="E26" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -1235,13 +1211,13 @@
         <v>29</v>
       </c>
       <c r="C27">
-        <v>3205434</v>
+        <v>3290379</v>
       </c>
       <c r="D27" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="E27" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -1252,13 +1228,13 @@
         <v>30</v>
       </c>
       <c r="C28">
-        <v>3205570</v>
+        <v>3290504</v>
       </c>
       <c r="D28" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="E28" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -1269,13 +1245,13 @@
         <v>31</v>
       </c>
       <c r="C29">
-        <v>3205496</v>
+        <v>3290712</v>
       </c>
       <c r="D29" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="E29" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -1286,13 +1262,13 @@
         <v>32</v>
       </c>
       <c r="C30">
-        <v>3565055</v>
+        <v>3290600</v>
       </c>
       <c r="D30" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="E30" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -1303,13 +1279,13 @@
         <v>33</v>
       </c>
       <c r="C31">
-        <v>3565090</v>
+        <v>3290825</v>
       </c>
       <c r="D31" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="E31" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -1320,13 +1296,13 @@
         <v>34</v>
       </c>
       <c r="C32">
-        <v>3565065</v>
+        <v>3290533</v>
       </c>
       <c r="D32" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="E32" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -1337,13 +1313,13 @@
         <v>35</v>
       </c>
       <c r="C33">
-        <v>3565100</v>
+        <v>3181163</v>
       </c>
       <c r="D33" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="E33" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -1354,13 +1330,13 @@
         <v>36</v>
       </c>
       <c r="C34">
-        <v>3560101</v>
+        <v>3180984</v>
       </c>
       <c r="D34" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="E34" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -1371,13 +1347,13 @@
         <v>37</v>
       </c>
       <c r="C35">
-        <v>3560127</v>
+        <v>3181407</v>
       </c>
       <c r="D35" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="E35" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -1388,13 +1364,13 @@
         <v>38</v>
       </c>
       <c r="C36">
-        <v>3185551</v>
+        <v>3185633</v>
       </c>
       <c r="D36" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="E36" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -1405,13 +1381,13 @@
         <v>39</v>
       </c>
       <c r="C37">
-        <v>3185137</v>
+        <v>3185885</v>
       </c>
       <c r="D37" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="E37" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -1422,13 +1398,13 @@
         <v>40</v>
       </c>
       <c r="C38">
-        <v>3185688</v>
+        <v>3185976</v>
       </c>
       <c r="D38" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="E38" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -1439,13 +1415,13 @@
         <v>41</v>
       </c>
       <c r="C39">
-        <v>3185579</v>
+        <v>3181239</v>
       </c>
       <c r="D39" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="E39" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
     </row>
     <row r="40" spans="1:5">
@@ -1456,13 +1432,13 @@
         <v>42</v>
       </c>
       <c r="C40">
-        <v>3185168</v>
+        <v>3180508</v>
       </c>
       <c r="D40" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="E40" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
     </row>
     <row r="41" spans="1:5">
@@ -1473,13 +1449,13 @@
         <v>43</v>
       </c>
       <c r="C41">
-        <v>3185705</v>
+        <v>3180557</v>
       </c>
       <c r="D41" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="E41" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
     </row>
     <row r="42" spans="1:5">
@@ -1490,13 +1466,13 @@
         <v>44</v>
       </c>
       <c r="C42">
-        <v>3185305</v>
+        <v>3181180</v>
       </c>
       <c r="D42" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="E42" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
     </row>
     <row r="43" spans="1:5">
@@ -1507,13 +1483,13 @@
         <v>45</v>
       </c>
       <c r="C43">
-        <v>3185702</v>
+        <v>3181408</v>
       </c>
       <c r="D43" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="E43" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
     </row>
     <row r="44" spans="1:5">
@@ -1524,13 +1500,13 @@
         <v>46</v>
       </c>
       <c r="C44">
-        <v>3185256</v>
+        <v>3180861</v>
       </c>
       <c r="D44" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="E44" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
     </row>
     <row r="45" spans="1:5">
@@ -1541,13 +1517,13 @@
         <v>47</v>
       </c>
       <c r="C45">
-        <v>3180990</v>
+        <v>3180535</v>
       </c>
       <c r="D45" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="E45" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
     </row>
     <row r="46" spans="1:5">
@@ -1558,13 +1534,13 @@
         <v>48</v>
       </c>
       <c r="C46">
-        <v>3180508</v>
+        <v>3181160</v>
       </c>
       <c r="D46" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="E46" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
     </row>
     <row r="47" spans="1:5">
@@ -1575,13 +1551,13 @@
         <v>49</v>
       </c>
       <c r="C47">
-        <v>3180557</v>
+        <v>3181273</v>
       </c>
       <c r="D47" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="E47" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
     </row>
     <row r="48" spans="1:5">
@@ -1592,13 +1568,13 @@
         <v>50</v>
       </c>
       <c r="C48">
-        <v>3180984</v>
+        <v>3181098</v>
       </c>
       <c r="D48" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="E48" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
     </row>
     <row r="49" spans="1:5">
@@ -1609,13 +1585,13 @@
         <v>51</v>
       </c>
       <c r="C49">
-        <v>3181180</v>
+        <v>3181007</v>
       </c>
       <c r="D49" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="E49" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
     </row>
     <row r="50" spans="1:5">
@@ -1626,13 +1602,13 @@
         <v>52</v>
       </c>
       <c r="C50">
-        <v>3181408</v>
+        <v>3180865</v>
       </c>
       <c r="D50" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="E50" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
     </row>
     <row r="51" spans="1:5">
@@ -1643,13 +1619,13 @@
         <v>53</v>
       </c>
       <c r="C51">
-        <v>3180861</v>
+        <v>3180838</v>
       </c>
       <c r="D51" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="E51" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
     </row>
     <row r="52" spans="1:5">
@@ -1660,13 +1636,13 @@
         <v>54</v>
       </c>
       <c r="C52">
-        <v>3180535</v>
+        <v>3181539</v>
       </c>
       <c r="D52" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="E52" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
     </row>
     <row r="53" spans="1:5">
@@ -1677,13 +1653,13 @@
         <v>55</v>
       </c>
       <c r="C53">
-        <v>3181160</v>
+        <v>3180990</v>
       </c>
       <c r="D53" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="E53" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
     </row>
     <row r="54" spans="1:5">
@@ -1694,13 +1670,13 @@
         <v>56</v>
       </c>
       <c r="C54">
-        <v>3181273</v>
+        <v>3185551</v>
       </c>
       <c r="D54" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="E54" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
     </row>
     <row r="55" spans="1:5">
@@ -1711,13 +1687,13 @@
         <v>57</v>
       </c>
       <c r="C55">
-        <v>3181098</v>
+        <v>3185137</v>
       </c>
       <c r="D55" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="E55" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
     </row>
     <row r="56" spans="1:5">
@@ -1728,13 +1704,13 @@
         <v>58</v>
       </c>
       <c r="C56">
-        <v>3181007</v>
+        <v>3185828</v>
       </c>
       <c r="D56" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="E56" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
     </row>
     <row r="57" spans="1:5">
@@ -1745,13 +1721,13 @@
         <v>59</v>
       </c>
       <c r="C57">
-        <v>3180865</v>
+        <v>3185447</v>
       </c>
       <c r="D57" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="E57" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
     </row>
     <row r="58" spans="1:5">
@@ -1762,13 +1738,13 @@
         <v>60</v>
       </c>
       <c r="C58">
-        <v>3290326</v>
+        <v>3185579</v>
       </c>
       <c r="D58" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="E58" t="s">
-        <v>134</v>
+        <v>127</v>
       </c>
     </row>
     <row r="59" spans="1:5">
@@ -1779,13 +1755,13 @@
         <v>61</v>
       </c>
       <c r="C59">
-        <v>3290379</v>
+        <v>3185911</v>
       </c>
       <c r="D59" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="E59" t="s">
-        <v>134</v>
+        <v>127</v>
       </c>
     </row>
     <row r="60" spans="1:5">
@@ -1796,13 +1772,13 @@
         <v>62</v>
       </c>
       <c r="C60">
-        <v>3290712</v>
+        <v>3185168</v>
       </c>
       <c r="D60" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="E60" t="s">
-        <v>134</v>
+        <v>127</v>
       </c>
     </row>
     <row r="61" spans="1:5">
@@ -1813,13 +1789,13 @@
         <v>63</v>
       </c>
       <c r="C61">
-        <v>3290616</v>
+        <v>3185705</v>
       </c>
       <c r="D61" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="E61" t="s">
-        <v>134</v>
+        <v>127</v>
       </c>
     </row>
     <row r="62" spans="1:5">
@@ -1830,13 +1806,13 @@
         <v>64</v>
       </c>
       <c r="C62">
-        <v>3290524</v>
+        <v>3185702</v>
       </c>
       <c r="D62" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="E62" t="s">
-        <v>134</v>
+        <v>127</v>
       </c>
     </row>
     <row r="63" spans="1:5">
@@ -1847,13 +1823,13 @@
         <v>65</v>
       </c>
       <c r="C63">
-        <v>3290245</v>
+        <v>3185256</v>
       </c>
       <c r="D63" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="E63" t="s">
-        <v>134</v>
+        <v>127</v>
       </c>
     </row>
     <row r="64" spans="1:5">
@@ -1864,13 +1840,13 @@
         <v>66</v>
       </c>
       <c r="C64">
-        <v>3290504</v>
+        <v>3185610</v>
       </c>
       <c r="D64" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="E64" t="s">
-        <v>134</v>
+        <v>127</v>
       </c>
     </row>
     <row r="65" spans="1:5">
@@ -1881,13 +1857,13 @@
         <v>67</v>
       </c>
       <c r="C65">
-        <v>3290407</v>
+        <v>3185562</v>
       </c>
       <c r="D65" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="E65" t="s">
-        <v>134</v>
+        <v>127</v>
       </c>
     </row>
     <row r="66" spans="1:5">
@@ -1898,13 +1874,13 @@
         <v>68</v>
       </c>
       <c r="C66">
-        <v>3290600</v>
+        <v>3185716</v>
       </c>
       <c r="D66" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="E66" t="s">
-        <v>134</v>
+        <v>127</v>
       </c>
     </row>
     <row r="67" spans="1:5">
@@ -1915,13 +1891,13 @@
         <v>69</v>
       </c>
       <c r="C67">
-        <v>3290533</v>
+        <v>3195219</v>
       </c>
       <c r="D67" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="E67" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
     </row>
     <row r="68" spans="1:5">
@@ -1932,13 +1908,13 @@
         <v>70</v>
       </c>
       <c r="C68">
-        <v>3290577</v>
+        <v>3195289</v>
       </c>
       <c r="D68" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="E68" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
     </row>
     <row r="69" spans="1:5">
@@ -1949,13 +1925,13 @@
         <v>71</v>
       </c>
       <c r="C69">
-        <v>3295241</v>
+        <v>3195253</v>
       </c>
       <c r="D69" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="E69" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
     </row>
     <row r="70" spans="1:5">
@@ -1966,13 +1942,13 @@
         <v>72</v>
       </c>
       <c r="C70">
-        <v>3295343</v>
+        <v>3195273</v>
       </c>
       <c r="D70" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="E70" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
     </row>
     <row r="71" spans="1:5">
@@ -1983,13 +1959,13 @@
         <v>73</v>
       </c>
       <c r="C71">
-        <v>3295370</v>
+        <v>3195263</v>
       </c>
       <c r="D71" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="E71" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
     </row>
     <row r="72" spans="1:5">
@@ -2000,13 +1976,13 @@
         <v>74</v>
       </c>
       <c r="C72">
-        <v>3295322</v>
+        <v>3190607</v>
       </c>
       <c r="D72" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="E72" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
     </row>
     <row r="73" spans="1:5">
@@ -2017,13 +1993,13 @@
         <v>75</v>
       </c>
       <c r="C73">
-        <v>3295283</v>
+        <v>3190323</v>
       </c>
       <c r="D73" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="E73" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
     </row>
     <row r="74" spans="1:5">
@@ -2034,13 +2010,13 @@
         <v>76</v>
       </c>
       <c r="C74">
-        <v>3295533</v>
+        <v>3190548</v>
       </c>
       <c r="D74" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="E74" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
     </row>
     <row r="75" spans="1:5">
@@ -2051,13 +2027,13 @@
         <v>77</v>
       </c>
       <c r="C75">
-        <v>3501976</v>
+        <v>3190282</v>
       </c>
       <c r="D75" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="E75" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
     </row>
     <row r="76" spans="1:5">
@@ -2068,13 +2044,13 @@
         <v>78</v>
       </c>
       <c r="C76">
-        <v>3500664</v>
+        <v>3190345</v>
       </c>
       <c r="D76" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="E76" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
     </row>
     <row r="77" spans="1:5">
@@ -2085,13 +2061,13 @@
         <v>79</v>
       </c>
       <c r="C77">
-        <v>3501340</v>
+        <v>3190529</v>
       </c>
       <c r="D77" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="E77" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
     </row>
     <row r="78" spans="1:5">
@@ -2102,13 +2078,13 @@
         <v>80</v>
       </c>
       <c r="C78">
-        <v>3501010</v>
+        <v>3190398</v>
       </c>
       <c r="D78" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="E78" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
     </row>
     <row r="79" spans="1:5">
@@ -2119,13 +2095,13 @@
         <v>81</v>
       </c>
       <c r="C79">
-        <v>3501555</v>
+        <v>3420605</v>
       </c>
       <c r="D79" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="E79" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
     </row>
     <row r="80" spans="1:5">
@@ -2136,13 +2112,13 @@
         <v>82</v>
       </c>
       <c r="C80">
-        <v>3505990</v>
+        <v>3420994</v>
       </c>
       <c r="D80" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="E80" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
     </row>
     <row r="81" spans="1:5">
@@ -2153,13 +2129,13 @@
         <v>83</v>
       </c>
       <c r="C81">
-        <v>3505800</v>
+        <v>3424235</v>
       </c>
       <c r="D81" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="E81" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
     </row>
     <row r="82" spans="1:5">
@@ -2170,13 +2146,13 @@
         <v>84</v>
       </c>
       <c r="C82">
-        <v>3506105</v>
+        <v>3422712</v>
       </c>
       <c r="D82" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="E82" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
     </row>
     <row r="83" spans="1:5">
@@ -2187,13 +2163,13 @@
         <v>85</v>
       </c>
       <c r="C83">
-        <v>3505998</v>
+        <v>3424611</v>
       </c>
       <c r="D83" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="E83" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
     </row>
     <row r="84" spans="1:5">
@@ -2204,13 +2180,13 @@
         <v>86</v>
       </c>
       <c r="C84">
-        <v>3506154</v>
+        <v>3424663</v>
       </c>
       <c r="D84" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="E84" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
     </row>
     <row r="85" spans="1:5">
@@ -2221,13 +2197,13 @@
         <v>87</v>
       </c>
       <c r="C85">
-        <v>3506079</v>
+        <v>3421845</v>
       </c>
       <c r="D85" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="E85" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
     </row>
     <row r="86" spans="1:5">
@@ -2238,13 +2214,13 @@
         <v>88</v>
       </c>
       <c r="C86">
-        <v>3506008</v>
+        <v>3424190</v>
       </c>
       <c r="D86" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="E86" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
     </row>
     <row r="87" spans="1:5">
@@ -2255,13 +2231,13 @@
         <v>89</v>
       </c>
       <c r="C87">
-        <v>3505809</v>
+        <v>3420909</v>
       </c>
       <c r="D87" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="E87" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
     </row>
     <row r="88" spans="1:5">
@@ -2272,13 +2248,13 @@
         <v>90</v>
       </c>
       <c r="C88">
-        <v>3506166</v>
+        <v>3422819</v>
       </c>
       <c r="D88" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="E88" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
     </row>
     <row r="89" spans="1:5">
@@ -2289,13 +2265,13 @@
         <v>91</v>
       </c>
       <c r="C89">
-        <v>3190323</v>
+        <v>3422477</v>
       </c>
       <c r="D89" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="E89" t="s">
-        <v>136</v>
+        <v>129</v>
       </c>
     </row>
     <row r="90" spans="1:5">
@@ -2306,13 +2282,13 @@
         <v>92</v>
       </c>
       <c r="C90">
-        <v>3190548</v>
+        <v>3421754</v>
       </c>
       <c r="D90" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="E90" t="s">
-        <v>136</v>
+        <v>129</v>
       </c>
     </row>
     <row r="91" spans="1:5">
@@ -2323,13 +2299,13 @@
         <v>93</v>
       </c>
       <c r="C91">
-        <v>3190429</v>
+        <v>3422619</v>
       </c>
       <c r="D91" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="E91" t="s">
-        <v>136</v>
+        <v>129</v>
       </c>
     </row>
     <row r="92" spans="1:5">
@@ -2340,13 +2316,13 @@
         <v>94</v>
       </c>
       <c r="C92">
-        <v>3190282</v>
+        <v>3422358</v>
       </c>
       <c r="D92" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="E92" t="s">
-        <v>136</v>
+        <v>129</v>
       </c>
     </row>
     <row r="93" spans="1:5">
@@ -2357,13 +2333,13 @@
         <v>95</v>
       </c>
       <c r="C93">
-        <v>3190345</v>
+        <v>8420246</v>
       </c>
       <c r="D93" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="E93" t="s">
-        <v>136</v>
+        <v>129</v>
       </c>
     </row>
     <row r="94" spans="1:5">
@@ -2374,13 +2350,13 @@
         <v>96</v>
       </c>
       <c r="C94">
-        <v>3190529</v>
+        <v>3424893</v>
       </c>
       <c r="D94" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="E94" t="s">
-        <v>136</v>
+        <v>129</v>
       </c>
     </row>
     <row r="95" spans="1:5">
@@ -2391,13 +2367,13 @@
         <v>97</v>
       </c>
       <c r="C95">
-        <v>3190398</v>
+        <v>3423627</v>
       </c>
       <c r="D95" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="E95" t="s">
-        <v>136</v>
+        <v>129</v>
       </c>
     </row>
     <row r="96" spans="1:5">
@@ -2408,13 +2384,13 @@
         <v>98</v>
       </c>
       <c r="C96">
-        <v>3190580</v>
+        <v>3422613</v>
       </c>
       <c r="D96" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="E96" t="s">
-        <v>136</v>
+        <v>129</v>
       </c>
     </row>
     <row r="97" spans="1:5">
@@ -2425,13 +2401,13 @@
         <v>99</v>
       </c>
       <c r="C97">
-        <v>3190302</v>
+        <v>3421779</v>
       </c>
       <c r="D97" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="E97" t="s">
-        <v>136</v>
+        <v>129</v>
       </c>
     </row>
     <row r="98" spans="1:5">
@@ -2442,13 +2418,13 @@
         <v>100</v>
       </c>
       <c r="C98">
-        <v>3195219</v>
+        <v>3425350</v>
       </c>
       <c r="D98" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="E98" t="s">
-        <v>136</v>
+        <v>129</v>
       </c>
     </row>
     <row r="99" spans="1:5">
@@ -2459,13 +2435,13 @@
         <v>101</v>
       </c>
       <c r="C99">
-        <v>3195289</v>
+        <v>3425499</v>
       </c>
       <c r="D99" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="E99" t="s">
-        <v>136</v>
+        <v>129</v>
       </c>
     </row>
     <row r="100" spans="1:5">
@@ -2476,13 +2452,13 @@
         <v>102</v>
       </c>
       <c r="C100">
-        <v>3195253</v>
+        <v>3426456</v>
       </c>
       <c r="D100" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="E100" t="s">
-        <v>136</v>
+        <v>129</v>
       </c>
     </row>
     <row r="101" spans="1:5">
@@ -2493,13 +2469,13 @@
         <v>103</v>
       </c>
       <c r="C101">
-        <v>3195273</v>
+        <v>3427126</v>
       </c>
       <c r="D101" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="E101" t="s">
-        <v>136</v>
+        <v>129</v>
       </c>
     </row>
     <row r="102" spans="1:5">
@@ -2510,13 +2486,13 @@
         <v>104</v>
       </c>
       <c r="C102">
-        <v>3195263</v>
+        <v>3427398</v>
       </c>
       <c r="D102" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="E102" t="s">
-        <v>136</v>
+        <v>129</v>
       </c>
     </row>
     <row r="103" spans="1:5">
@@ -2527,13 +2503,13 @@
         <v>105</v>
       </c>
       <c r="C103">
-        <v>3423264</v>
+        <v>3425530</v>
       </c>
       <c r="D103" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="E103" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
     </row>
     <row r="104" spans="1:5">
@@ -2544,13 +2520,13 @@
         <v>106</v>
       </c>
       <c r="C104">
-        <v>3424235</v>
+        <v>3426852</v>
       </c>
       <c r="D104" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="E104" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
     </row>
     <row r="105" spans="1:5">
@@ -2561,13 +2537,13 @@
         <v>107</v>
       </c>
       <c r="C105">
-        <v>3420586</v>
+        <v>3423264</v>
       </c>
       <c r="D105" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="E105" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
     </row>
     <row r="106" spans="1:5">
@@ -2578,13 +2554,13 @@
         <v>108</v>
       </c>
       <c r="C106">
-        <v>3421779</v>
+        <v>3424269</v>
       </c>
       <c r="D106" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="E106" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
     </row>
     <row r="107" spans="1:5">
@@ -2595,13 +2571,13 @@
         <v>109</v>
       </c>
       <c r="C107">
-        <v>3420605</v>
+        <v>3424685</v>
       </c>
       <c r="D107" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="E107" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
     </row>
     <row r="108" spans="1:5">
@@ -2612,13 +2588,13 @@
         <v>110</v>
       </c>
       <c r="C108">
-        <v>3420994</v>
+        <v>3426849</v>
       </c>
       <c r="D108" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="E108" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
     </row>
     <row r="109" spans="1:5">
@@ -2629,13 +2605,13 @@
         <v>111</v>
       </c>
       <c r="C109">
-        <v>3425896</v>
+        <v>3426200</v>
       </c>
       <c r="D109" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="E109" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
     </row>
     <row r="110" spans="1:5">
@@ -2646,13 +2622,13 @@
         <v>112</v>
       </c>
       <c r="C110">
-        <v>3425499</v>
+        <v>3427972</v>
       </c>
       <c r="D110" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="E110" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
     </row>
     <row r="111" spans="1:5">
@@ -2663,13 +2639,13 @@
         <v>113</v>
       </c>
       <c r="C111">
-        <v>3425410</v>
+        <v>3426712</v>
       </c>
       <c r="D111" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="E111" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
     </row>
     <row r="112" spans="1:5">
@@ -2680,13 +2656,13 @@
         <v>114</v>
       </c>
       <c r="C112">
-        <v>3424685</v>
+        <v>3426278</v>
       </c>
       <c r="D112" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="E112" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
     </row>
     <row r="113" spans="1:5">
@@ -2697,13 +2673,13 @@
         <v>115</v>
       </c>
       <c r="C113">
-        <v>3422819</v>
+        <v>3427704</v>
       </c>
       <c r="D113" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="E113" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
     </row>
     <row r="114" spans="1:5">
@@ -2714,13 +2690,13 @@
         <v>116</v>
       </c>
       <c r="C114">
-        <v>3422477</v>
+        <v>3427352</v>
       </c>
       <c r="D114" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="E114" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
     </row>
     <row r="115" spans="1:5">
@@ -2731,13 +2707,13 @@
         <v>117</v>
       </c>
       <c r="C115">
-        <v>3421164</v>
+        <v>3425381</v>
       </c>
       <c r="D115" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="E115" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
     </row>
     <row r="116" spans="1:5">
@@ -2748,13 +2724,13 @@
         <v>118</v>
       </c>
       <c r="C116">
-        <v>3421754</v>
+        <v>3426149</v>
       </c>
       <c r="D116" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="E116" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
     </row>
     <row r="117" spans="1:5">
@@ -2765,13 +2741,13 @@
         <v>119</v>
       </c>
       <c r="C117">
-        <v>3422619</v>
+        <v>3425669</v>
       </c>
       <c r="D117" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="E117" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
     </row>
     <row r="118" spans="1:5">
@@ -2782,13 +2758,13 @@
         <v>120</v>
       </c>
       <c r="C118">
-        <v>3426852</v>
+        <v>3426496</v>
       </c>
       <c r="D118" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="E118" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
     </row>
     <row r="119" spans="1:5">
@@ -2799,13 +2775,13 @@
         <v>121</v>
       </c>
       <c r="C119">
-        <v>3427352</v>
+        <v>3426626</v>
       </c>
       <c r="D119" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="E119" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
     </row>
     <row r="120" spans="1:5">
@@ -2816,64 +2792,13 @@
         <v>122</v>
       </c>
       <c r="C120">
-        <v>3426496</v>
+        <v>3426112</v>
       </c>
       <c r="D120" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="E120" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="121" spans="1:5">
-      <c r="A121" s="1">
-        <v>119</v>
-      </c>
-      <c r="B121" t="s">
-        <v>123</v>
-      </c>
-      <c r="C121">
-        <v>3426811</v>
-      </c>
-      <c r="D121" t="s">
-        <v>127</v>
-      </c>
-      <c r="E121" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="122" spans="1:5">
-      <c r="A122" s="1">
-        <v>120</v>
-      </c>
-      <c r="B122" t="s">
-        <v>124</v>
-      </c>
-      <c r="C122">
-        <v>3426112</v>
-      </c>
-      <c r="D122" t="s">
-        <v>127</v>
-      </c>
-      <c r="E122" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="123" spans="1:5">
-      <c r="A123" s="1">
-        <v>121</v>
-      </c>
-      <c r="B123" t="s">
-        <v>125</v>
-      </c>
-      <c r="C123">
-        <v>3425669</v>
-      </c>
-      <c r="D123" t="s">
-        <v>127</v>
-      </c>
-      <c r="E123" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
     </row>
   </sheetData>
